--- a/backend/data/financials_by_company/1912.HK.xlsx
+++ b/backend/data/financials_by_company/1912.HK.xlsx
@@ -657,16 +657,16 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.165</v>
+        <v>0.12671</v>
       </c>
       <c r="D2" t="n">
-        <v>-3700000</v>
+        <v>4950000</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -675,423 +675,421 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-7948000</v>
+        <v>2171000</v>
       </c>
       <c r="H2" t="n">
-        <v>951000</v>
+        <v>647000</v>
       </c>
       <c r="I2" t="n">
-        <v>60046000</v>
+        <v>209452000</v>
       </c>
       <c r="J2" t="n">
-        <v>-3700000</v>
+        <v>4950000</v>
       </c>
       <c r="K2" t="n">
-        <v>-4651000</v>
+        <v>4303000</v>
       </c>
       <c r="L2" t="n">
-        <v>-3053000</v>
+        <v>-1772000</v>
       </c>
       <c r="M2" t="n">
-        <v>3113000</v>
+        <v>1817000</v>
       </c>
       <c r="N2" t="n">
-        <v>60000</v>
+        <v>45000</v>
       </c>
       <c r="O2" t="n">
-        <v>-7948000</v>
+        <v>2171000</v>
       </c>
       <c r="P2" t="n">
-        <v>-7948000</v>
+        <v>2171000</v>
       </c>
       <c r="Q2" t="n">
-        <v>67148000</v>
+        <v>217966000</v>
       </c>
       <c r="R2" t="n">
-        <v>141000</v>
+        <v>12000</v>
       </c>
       <c r="S2" t="n">
-        <v>1098122000</v>
+        <v>80842100</v>
       </c>
       <c r="T2" t="n">
-        <v>1098122000</v>
+        <v>80842100</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0072</v>
+        <v>0.208</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0072</v>
+        <v>0.208</v>
       </c>
       <c r="W2" t="n">
-        <v>-7948000</v>
+        <v>2171000</v>
       </c>
       <c r="X2" t="n">
-        <v>-7948000</v>
+        <v>2171000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-7948000</v>
+        <v>2171000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-7948000</v>
+        <v>2171000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-7948000</v>
+        <v>2171000</v>
       </c>
       <c r="AC2" t="n">
-        <v>184000</v>
+        <v>315000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-7764000</v>
+        <v>2486000</v>
       </c>
       <c r="AE2" t="n">
-        <v>18000</v>
+        <v>46000</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
       <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>-3053000</v>
+        <v>-1772000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3113000</v>
+        <v>1817000</v>
       </c>
       <c r="AK2" t="n">
-        <v>60000</v>
+        <v>45000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-4729000</v>
+        <v>4074000</v>
       </c>
       <c r="AM2" t="n">
-        <v>7102000</v>
+        <v>8514000</v>
       </c>
       <c r="AN2" t="n">
-        <v>100000</v>
+        <v>89000</v>
       </c>
       <c r="AO2" t="n">
-        <v>7002000</v>
+        <v>8442000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1917000</v>
+        <v>3213000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5085000</v>
+        <v>5229000</v>
       </c>
       <c r="AR2" t="n">
-        <v>2373000</v>
+        <v>12588000</v>
       </c>
       <c r="AS2" t="n">
-        <v>60046000</v>
+        <v>209452000</v>
       </c>
       <c r="AT2" t="n">
-        <v>62419000</v>
+        <v>222040000</v>
       </c>
       <c r="AU2" t="n">
-        <v>62419000</v>
+        <v>222040000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-75405</v>
+        <v>7595.570534</v>
       </c>
       <c r="C3" t="n">
-        <v>0.165</v>
+        <v>0.237362</v>
       </c>
       <c r="D3" t="n">
-        <v>-5363000</v>
+        <v>92000</v>
       </c>
       <c r="E3" t="n">
-        <v>-200000</v>
+        <v>32000</v>
       </c>
       <c r="F3" t="n">
-        <v>-457000</v>
+        <v>32000</v>
       </c>
       <c r="G3" t="n">
-        <v>-9749000</v>
+        <v>-1584000</v>
       </c>
       <c r="H3" t="n">
-        <v>802000</v>
+        <v>646000</v>
       </c>
       <c r="I3" t="n">
-        <v>63382000</v>
+        <v>113314000</v>
       </c>
       <c r="J3" t="n">
-        <v>-5563000</v>
+        <v>124000</v>
       </c>
       <c r="K3" t="n">
-        <v>-6365000</v>
+        <v>-522000</v>
       </c>
       <c r="L3" t="n">
-        <v>-2164000</v>
+        <v>-1470000</v>
       </c>
       <c r="M3" t="n">
-        <v>2284000</v>
+        <v>1555000</v>
       </c>
       <c r="N3" t="n">
-        <v>120000</v>
+        <v>85000</v>
       </c>
       <c r="O3" t="n">
-        <v>-9110405</v>
+        <v>-1608404.429466</v>
       </c>
       <c r="P3" t="n">
-        <v>-9749000</v>
+        <v>-1584000</v>
       </c>
       <c r="Q3" t="n">
-        <v>72365000</v>
+        <v>122369000</v>
       </c>
       <c r="R3" t="n">
-        <v>36000</v>
+        <v>13000</v>
       </c>
       <c r="S3" t="n">
-        <v>109812200</v>
+        <v>81168800</v>
       </c>
       <c r="T3" t="n">
-        <v>109812200</v>
+        <v>81168800</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.089</v>
+        <v>-0.151</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.089</v>
+        <v>-0.151</v>
       </c>
       <c r="W3" t="n">
-        <v>-9749000</v>
+        <v>-1584000</v>
       </c>
       <c r="X3" t="n">
-        <v>-9749000</v>
+        <v>-1584000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-9749000</v>
+        <v>-1584000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-9749000</v>
+        <v>-1584000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-9749000</v>
+        <v>-1584000</v>
       </c>
       <c r="AC3" t="n">
-        <v>1100000</v>
+        <v>-493000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-8649000</v>
+        <v>-2077000</v>
       </c>
       <c r="AE3" t="n">
-        <v>21000</v>
+        <v>20000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-457000</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+        <v>32000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-32000</v>
+      </c>
       <c r="AH3" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-2164000</v>
+        <v>-1470000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2284000</v>
+        <v>1555000</v>
       </c>
       <c r="AK3" t="n">
-        <v>120000</v>
+        <v>85000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-6049000</v>
+        <v>-659000</v>
       </c>
       <c r="AM3" t="n">
-        <v>8983000</v>
+        <v>9055000</v>
       </c>
       <c r="AN3" t="n">
-        <v>242000</v>
+        <v>465000</v>
       </c>
       <c r="AO3" t="n">
-        <v>8793000</v>
+        <v>8682000</v>
       </c>
       <c r="AP3" t="n">
-        <v>2959000</v>
+        <v>3337000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5834000</v>
+        <v>5345000</v>
       </c>
       <c r="AR3" t="n">
-        <v>2934000</v>
+        <v>8396000</v>
       </c>
       <c r="AS3" t="n">
-        <v>63382000</v>
+        <v>113314000</v>
       </c>
       <c r="AT3" t="n">
-        <v>66316000</v>
+        <v>121710000</v>
       </c>
       <c r="AU3" t="n">
-        <v>66316000</v>
+        <v>121710000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>7595.570534</v>
+        <v>-75405</v>
       </c>
       <c r="C4" t="n">
-        <v>0.237362</v>
+        <v>0.165</v>
       </c>
       <c r="D4" t="n">
-        <v>92000</v>
+        <v>-5363000</v>
       </c>
       <c r="E4" t="n">
-        <v>32000</v>
+        <v>-200000</v>
       </c>
       <c r="F4" t="n">
-        <v>32000</v>
+        <v>-457000</v>
       </c>
       <c r="G4" t="n">
-        <v>-1584000</v>
+        <v>-9749000</v>
       </c>
       <c r="H4" t="n">
-        <v>646000</v>
+        <v>802000</v>
       </c>
       <c r="I4" t="n">
-        <v>113314000</v>
+        <v>63382000</v>
       </c>
       <c r="J4" t="n">
-        <v>124000</v>
+        <v>-5563000</v>
       </c>
       <c r="K4" t="n">
-        <v>-522000</v>
+        <v>-6365000</v>
       </c>
       <c r="L4" t="n">
-        <v>-1470000</v>
+        <v>-2164000</v>
       </c>
       <c r="M4" t="n">
-        <v>1555000</v>
+        <v>2284000</v>
       </c>
       <c r="N4" t="n">
-        <v>85000</v>
+        <v>120000</v>
       </c>
       <c r="O4" t="n">
-        <v>-1608404.429466</v>
+        <v>-9110405</v>
       </c>
       <c r="P4" t="n">
-        <v>-1584000</v>
+        <v>-9749000</v>
       </c>
       <c r="Q4" t="n">
-        <v>122369000</v>
+        <v>72365000</v>
       </c>
       <c r="R4" t="n">
-        <v>13000</v>
+        <v>36000</v>
       </c>
       <c r="S4" t="n">
-        <v>81168800</v>
+        <v>109812200</v>
       </c>
       <c r="T4" t="n">
-        <v>81168800</v>
+        <v>109812200</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.151</v>
+        <v>-0.089</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.151</v>
+        <v>-0.089</v>
       </c>
       <c r="W4" t="n">
-        <v>-1584000</v>
+        <v>-9749000</v>
       </c>
       <c r="X4" t="n">
-        <v>-1584000</v>
+        <v>-9749000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1584000</v>
+        <v>-9749000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1584000</v>
+        <v>-9749000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1584000</v>
+        <v>-9749000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-493000</v>
+        <v>1100000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-2077000</v>
+        <v>-8649000</v>
       </c>
       <c r="AE4" t="n">
-        <v>20000</v>
+        <v>21000</v>
       </c>
       <c r="AF4" t="n">
-        <v>32000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-32000</v>
-      </c>
+        <v>-457000</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1470000</v>
+        <v>-2164000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1555000</v>
+        <v>2284000</v>
       </c>
       <c r="AK4" t="n">
-        <v>85000</v>
+        <v>120000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-659000</v>
+        <v>-6049000</v>
       </c>
       <c r="AM4" t="n">
-        <v>9055000</v>
+        <v>8983000</v>
       </c>
       <c r="AN4" t="n">
-        <v>465000</v>
+        <v>242000</v>
       </c>
       <c r="AO4" t="n">
-        <v>8682000</v>
+        <v>8793000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3337000</v>
+        <v>2959000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5345000</v>
+        <v>5834000</v>
       </c>
       <c r="AR4" t="n">
-        <v>8396000</v>
+        <v>2934000</v>
       </c>
       <c r="AS4" t="n">
-        <v>113314000</v>
+        <v>63382000</v>
       </c>
       <c r="AT4" t="n">
-        <v>121710000</v>
+        <v>66316000</v>
       </c>
       <c r="AU4" t="n">
-        <v>121710000</v>
+        <v>66316000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.12671</v>
+        <v>0.165</v>
       </c>
       <c r="D5" t="n">
-        <v>4950000</v>
+        <v>-3700000</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1100,123 +1098,125 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2171000</v>
+        <v>-7948000</v>
       </c>
       <c r="H5" t="n">
-        <v>647000</v>
+        <v>951000</v>
       </c>
       <c r="I5" t="n">
-        <v>209452000</v>
+        <v>60046000</v>
       </c>
       <c r="J5" t="n">
-        <v>4950000</v>
+        <v>-3700000</v>
       </c>
       <c r="K5" t="n">
-        <v>4303000</v>
+        <v>-4651000</v>
       </c>
       <c r="L5" t="n">
-        <v>-1772000</v>
+        <v>-3053000</v>
       </c>
       <c r="M5" t="n">
-        <v>1817000</v>
+        <v>3113000</v>
       </c>
       <c r="N5" t="n">
-        <v>45000</v>
+        <v>60000</v>
       </c>
       <c r="O5" t="n">
-        <v>2171000</v>
+        <v>-7948000</v>
       </c>
       <c r="P5" t="n">
-        <v>2171000</v>
+        <v>-7948000</v>
       </c>
       <c r="Q5" t="n">
-        <v>217966000</v>
+        <v>67148000</v>
       </c>
       <c r="R5" t="n">
-        <v>12000</v>
+        <v>141000</v>
       </c>
       <c r="S5" t="n">
-        <v>80842100</v>
+        <v>1098122000</v>
       </c>
       <c r="T5" t="n">
-        <v>80842100</v>
+        <v>1098122000</v>
       </c>
       <c r="U5" t="n">
-        <v>0.208</v>
+        <v>-0.0072</v>
       </c>
       <c r="V5" t="n">
-        <v>0.208</v>
+        <v>-0.0072</v>
       </c>
       <c r="W5" t="n">
-        <v>2171000</v>
+        <v>-7948000</v>
       </c>
       <c r="X5" t="n">
-        <v>2171000</v>
+        <v>-7948000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2171000</v>
+        <v>-7948000</v>
       </c>
       <c r="AA5" t="n">
-        <v>2171000</v>
+        <v>-7948000</v>
       </c>
       <c r="AB5" t="n">
-        <v>2171000</v>
+        <v>-7948000</v>
       </c>
       <c r="AC5" t="n">
-        <v>315000</v>
+        <v>184000</v>
       </c>
       <c r="AD5" t="n">
-        <v>2486000</v>
+        <v>-7764000</v>
       </c>
       <c r="AE5" t="n">
-        <v>46000</v>
+        <v>18000</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
       <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
       <c r="AI5" t="n">
-        <v>-1772000</v>
+        <v>-3053000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1817000</v>
+        <v>3113000</v>
       </c>
       <c r="AK5" t="n">
-        <v>45000</v>
+        <v>60000</v>
       </c>
       <c r="AL5" t="n">
-        <v>4074000</v>
+        <v>-4729000</v>
       </c>
       <c r="AM5" t="n">
-        <v>8514000</v>
+        <v>7102000</v>
       </c>
       <c r="AN5" t="n">
-        <v>89000</v>
+        <v>100000</v>
       </c>
       <c r="AO5" t="n">
-        <v>8442000</v>
+        <v>7002000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3213000</v>
+        <v>1917000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5229000</v>
+        <v>5085000</v>
       </c>
       <c r="AR5" t="n">
-        <v>12588000</v>
+        <v>2373000</v>
       </c>
       <c r="AS5" t="n">
-        <v>209452000</v>
+        <v>60046000</v>
       </c>
       <c r="AT5" t="n">
-        <v>222040000</v>
+        <v>62419000</v>
       </c>
       <c r="AU5" t="n">
-        <v>222040000</v>
+        <v>62419000</v>
       </c>
     </row>
   </sheetData>
@@ -1542,171 +1542,189 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>109812238</v>
+        <v>84651162</v>
       </c>
       <c r="C2" t="n">
-        <v>109812238</v>
+        <v>84651162</v>
       </c>
       <c r="D2" t="n">
-        <v>12618000</v>
+        <v>9477000</v>
       </c>
       <c r="E2" t="n">
-        <v>15491000</v>
+        <v>17558000</v>
       </c>
       <c r="F2" t="n">
-        <v>10089000</v>
+        <v>34026000</v>
       </c>
       <c r="G2" t="n">
-        <v>30296000</v>
+        <v>51479000</v>
       </c>
       <c r="H2" t="n">
-        <v>4674000</v>
+        <v>25433000</v>
       </c>
       <c r="I2" t="n">
-        <v>10089000</v>
+        <v>34026000</v>
       </c>
       <c r="J2" t="n">
-        <v>316000</v>
+        <v>411000</v>
       </c>
       <c r="K2" t="n">
-        <v>15121000</v>
+        <v>34332000</v>
       </c>
       <c r="L2" t="n">
-        <v>16403000</v>
+        <v>34332000</v>
       </c>
       <c r="M2" t="n">
-        <v>15121000</v>
+        <v>34332000</v>
       </c>
       <c r="N2" t="n">
-        <v>15121000</v>
+        <v>34332000</v>
       </c>
       <c r="O2" t="n">
-        <v>-2852000</v>
+        <v>16436000</v>
       </c>
       <c r="P2" t="n">
-        <v>14700000</v>
+        <v>12793000</v>
       </c>
       <c r="Q2" t="n">
-        <v>1417000</v>
+        <v>1032000</v>
       </c>
       <c r="R2" t="n">
-        <v>1417000</v>
+        <v>1032000</v>
       </c>
       <c r="S2" t="n">
-        <v>34136000</v>
+        <v>42868000</v>
       </c>
       <c r="T2" t="n">
-        <v>1972000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>588000</v>
-      </c>
+        <v>160000</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>1384000</v>
+        <v>160000</v>
       </c>
       <c r="W2" t="n">
-        <v>102000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1282000</v>
-      </c>
+        <v>160000</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>32164000</v>
+        <v>42708000</v>
       </c>
       <c r="Z2" t="n">
-        <v>14107000</v>
+        <v>17398000</v>
       </c>
       <c r="AA2" t="n">
-        <v>214000</v>
+        <v>251000</v>
       </c>
       <c r="AB2" t="n">
-        <v>13893000</v>
+        <v>17147000</v>
       </c>
       <c r="AC2" t="n">
-        <v>13029000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+        <v>24211000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>555000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>368000</v>
+      </c>
       <c r="AF2" t="n">
-        <v>13029000</v>
+        <v>23288000</v>
       </c>
       <c r="AG2" t="n">
-        <v>49257000</v>
+        <v>77200000</v>
       </c>
       <c r="AH2" t="n">
-        <v>12419000</v>
+        <v>9059000</v>
       </c>
       <c r="AI2" t="n">
-        <v>2493000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+        <v>1465000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>89000</v>
+      </c>
       <c r="AK2" t="n">
-        <v>4255000</v>
+        <v>6281000</v>
       </c>
       <c r="AL2" t="n">
-        <v>4255000</v>
+        <v>6281000</v>
       </c>
       <c r="AM2" t="n">
-        <v>5032000</v>
+        <v>306000</v>
       </c>
       <c r="AN2" t="n">
-        <v>5032000</v>
+        <v>20000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>286000</v>
       </c>
       <c r="AP2" t="n">
-        <v>639000</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
+        <v>918000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-1173000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2091000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1002000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>969000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>120000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
       <c r="AW2" t="n">
-        <v>36838000</v>
+        <v>68141000</v>
       </c>
       <c r="AX2" t="n">
-        <v>1031000</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+        <v>1245000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>2047000</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>12030000</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
+        <v>14359000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>14359000</v>
+      </c>
       <c r="BB2" t="n">
-        <v>11258000</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
+        <v>5102000</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>736000</v>
+      </c>
       <c r="BD2" t="n">
-        <v>9962000</v>
+        <v>36982000</v>
       </c>
       <c r="BE2" t="n">
-        <v>-1277000</v>
+        <v>-483000</v>
       </c>
       <c r="BF2" t="n">
-        <v>11239000</v>
+        <v>37465000</v>
       </c>
       <c r="BG2" t="n">
-        <v>2557000</v>
+        <v>7670000</v>
       </c>
       <c r="BH2" t="n">
-        <v>2557000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>138000</v>
-      </c>
+        <v>7670000</v>
+      </c>
+      <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="n">
-        <v>2419000</v>
+        <v>7670000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>109812238</v>
@@ -1715,40 +1733,40 @@
         <v>109812238</v>
       </c>
       <c r="D3" t="n">
-        <v>18029000</v>
+        <v>8763000</v>
       </c>
       <c r="E3" t="n">
-        <v>20745000</v>
+        <v>11595000</v>
       </c>
       <c r="F3" t="n">
-        <v>19106000</v>
+        <v>32387000</v>
       </c>
       <c r="G3" t="n">
-        <v>43162000</v>
+        <v>45584000</v>
       </c>
       <c r="H3" t="n">
-        <v>11966000</v>
+        <v>22040000</v>
       </c>
       <c r="I3" t="n">
-        <v>19106000</v>
+        <v>32387000</v>
       </c>
       <c r="J3" t="n">
-        <v>180000</v>
+        <v>489000</v>
       </c>
       <c r="K3" t="n">
-        <v>22597000</v>
+        <v>34478000</v>
       </c>
       <c r="L3" t="n">
-        <v>22597000</v>
+        <v>34478000</v>
       </c>
       <c r="M3" t="n">
-        <v>22597000</v>
+        <v>34478000</v>
       </c>
       <c r="N3" t="n">
-        <v>22597000</v>
+        <v>34478000</v>
       </c>
       <c r="O3" t="n">
-        <v>5096000</v>
+        <v>14845000</v>
       </c>
       <c r="P3" t="n">
         <v>14700000</v>
@@ -1760,137 +1778,137 @@
         <v>1417000</v>
       </c>
       <c r="S3" t="n">
-        <v>31592000</v>
+        <v>31327000</v>
       </c>
       <c r="T3" t="n">
-        <v>415000</v>
+        <v>108000</v>
       </c>
       <c r="U3" t="n">
-        <v>415000</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>108000</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
+        <v>108000</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>31177000</v>
+        <v>31219000</v>
       </c>
       <c r="Z3" t="n">
-        <v>20745000</v>
+        <v>11487000</v>
       </c>
       <c r="AA3" t="n">
-        <v>180000</v>
+        <v>381000</v>
       </c>
       <c r="AB3" t="n">
-        <v>20565000</v>
+        <v>11106000</v>
       </c>
       <c r="AC3" t="n">
-        <v>9290000</v>
+        <v>18450000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1649000</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
+        <v>334000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
       <c r="AF3" t="n">
-        <v>7641000</v>
+        <v>18116000</v>
       </c>
       <c r="AG3" t="n">
-        <v>54189000</v>
+        <v>65805000</v>
       </c>
       <c r="AH3" t="n">
-        <v>11046000</v>
+        <v>12546000</v>
       </c>
       <c r="AI3" t="n">
-        <v>2734000</v>
+        <v>2671000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>680000</v>
       </c>
       <c r="AK3" t="n">
-        <v>4255000</v>
+        <v>6293000</v>
       </c>
       <c r="AL3" t="n">
-        <v>4255000</v>
+        <v>6293000</v>
       </c>
       <c r="AM3" t="n">
-        <v>3491000</v>
+        <v>2091000</v>
       </c>
       <c r="AN3" t="n">
-        <v>3491000</v>
+        <v>1831000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>260000</v>
       </c>
       <c r="AP3" t="n">
-        <v>566000</v>
+        <v>811000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-1578000</v>
+        <v>-1056000</v>
       </c>
       <c r="AR3" t="n">
-        <v>2144000</v>
+        <v>1867000</v>
       </c>
       <c r="AS3" t="n">
-        <v>801000</v>
+        <v>897000</v>
       </c>
       <c r="AT3" t="n">
-        <v>869000</v>
+        <v>859000</v>
       </c>
       <c r="AU3" t="n">
-        <v>474000</v>
+        <v>111000</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>43143000</v>
+        <v>53259000</v>
       </c>
       <c r="AX3" t="n">
-        <v>379000</v>
+        <v>902000</v>
       </c>
       <c r="AY3" t="n">
-        <v>3519000</v>
+        <v>2236000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14007000</v>
+        <v>20062000</v>
       </c>
       <c r="BA3" t="n">
-        <v>14007000</v>
+        <v>20062000</v>
       </c>
       <c r="BB3" t="n">
-        <v>6425000</v>
+        <v>7231000</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>224000</v>
       </c>
       <c r="BD3" t="n">
-        <v>16277000</v>
+        <v>20261000</v>
       </c>
       <c r="BE3" t="n">
-        <v>-1180000</v>
+        <v>-939000</v>
       </c>
       <c r="BF3" t="n">
-        <v>17457000</v>
+        <v>21200000</v>
       </c>
       <c r="BG3" t="n">
-        <v>2536000</v>
+        <v>2343000</v>
       </c>
       <c r="BH3" t="n">
-        <v>2536000</v>
+        <v>2343000</v>
       </c>
       <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="n">
-        <v>2536000</v>
+        <v>2343000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>109812238</v>
@@ -1899,40 +1917,40 @@
         <v>109812238</v>
       </c>
       <c r="D4" t="n">
-        <v>8763000</v>
+        <v>18029000</v>
       </c>
       <c r="E4" t="n">
-        <v>11595000</v>
+        <v>20745000</v>
       </c>
       <c r="F4" t="n">
-        <v>32387000</v>
+        <v>19106000</v>
       </c>
       <c r="G4" t="n">
-        <v>45584000</v>
+        <v>43162000</v>
       </c>
       <c r="H4" t="n">
-        <v>22040000</v>
+        <v>11966000</v>
       </c>
       <c r="I4" t="n">
-        <v>32387000</v>
+        <v>19106000</v>
       </c>
       <c r="J4" t="n">
-        <v>489000</v>
+        <v>180000</v>
       </c>
       <c r="K4" t="n">
-        <v>34478000</v>
+        <v>22597000</v>
       </c>
       <c r="L4" t="n">
-        <v>34478000</v>
+        <v>22597000</v>
       </c>
       <c r="M4" t="n">
-        <v>34478000</v>
+        <v>22597000</v>
       </c>
       <c r="N4" t="n">
-        <v>34478000</v>
+        <v>22597000</v>
       </c>
       <c r="O4" t="n">
-        <v>14845000</v>
+        <v>5096000</v>
       </c>
       <c r="P4" t="n">
         <v>14700000</v>
@@ -1944,314 +1962,296 @@
         <v>1417000</v>
       </c>
       <c r="S4" t="n">
-        <v>31327000</v>
+        <v>31592000</v>
       </c>
       <c r="T4" t="n">
-        <v>108000</v>
+        <v>415000</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>415000</v>
       </c>
       <c r="V4" t="n">
-        <v>108000</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>108000</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
       <c r="Y4" t="n">
-        <v>31219000</v>
+        <v>31177000</v>
       </c>
       <c r="Z4" t="n">
-        <v>11487000</v>
+        <v>20745000</v>
       </c>
       <c r="AA4" t="n">
-        <v>381000</v>
+        <v>180000</v>
       </c>
       <c r="AB4" t="n">
-        <v>11106000</v>
+        <v>20565000</v>
       </c>
       <c r="AC4" t="n">
-        <v>18450000</v>
+        <v>9290000</v>
       </c>
       <c r="AD4" t="n">
-        <v>334000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
+        <v>1649000</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>18116000</v>
+        <v>7641000</v>
       </c>
       <c r="AG4" t="n">
-        <v>65805000</v>
+        <v>54189000</v>
       </c>
       <c r="AH4" t="n">
-        <v>12546000</v>
+        <v>11046000</v>
       </c>
       <c r="AI4" t="n">
-        <v>2671000</v>
+        <v>2734000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>680000</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>6293000</v>
+        <v>4255000</v>
       </c>
       <c r="AL4" t="n">
-        <v>6293000</v>
+        <v>4255000</v>
       </c>
       <c r="AM4" t="n">
-        <v>2091000</v>
+        <v>3491000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1831000</v>
+        <v>3491000</v>
       </c>
       <c r="AO4" t="n">
-        <v>260000</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>811000</v>
+        <v>566000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1056000</v>
+        <v>-1578000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1867000</v>
+        <v>2144000</v>
       </c>
       <c r="AS4" t="n">
-        <v>897000</v>
+        <v>801000</v>
       </c>
       <c r="AT4" t="n">
-        <v>859000</v>
+        <v>869000</v>
       </c>
       <c r="AU4" t="n">
-        <v>111000</v>
+        <v>474000</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>53259000</v>
+        <v>43143000</v>
       </c>
       <c r="AX4" t="n">
-        <v>902000</v>
+        <v>379000</v>
       </c>
       <c r="AY4" t="n">
-        <v>2236000</v>
+        <v>3519000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20062000</v>
+        <v>14007000</v>
       </c>
       <c r="BA4" t="n">
-        <v>20062000</v>
+        <v>14007000</v>
       </c>
       <c r="BB4" t="n">
-        <v>7231000</v>
+        <v>6425000</v>
       </c>
       <c r="BC4" t="n">
-        <v>224000</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>20261000</v>
+        <v>16277000</v>
       </c>
       <c r="BE4" t="n">
-        <v>-939000</v>
+        <v>-1180000</v>
       </c>
       <c r="BF4" t="n">
-        <v>21200000</v>
+        <v>17457000</v>
       </c>
       <c r="BG4" t="n">
-        <v>2343000</v>
+        <v>2536000</v>
       </c>
       <c r="BH4" t="n">
-        <v>2343000</v>
+        <v>2536000</v>
       </c>
       <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="n">
-        <v>2343000</v>
+        <v>2536000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>84651162</v>
+        <v>109812238</v>
       </c>
       <c r="C5" t="n">
-        <v>84651162</v>
+        <v>109812238</v>
       </c>
       <c r="D5" t="n">
-        <v>9477000</v>
+        <v>12618000</v>
       </c>
       <c r="E5" t="n">
-        <v>17558000</v>
+        <v>15491000</v>
       </c>
       <c r="F5" t="n">
-        <v>34026000</v>
+        <v>10089000</v>
       </c>
       <c r="G5" t="n">
-        <v>51479000</v>
+        <v>30296000</v>
       </c>
       <c r="H5" t="n">
-        <v>25433000</v>
+        <v>4674000</v>
       </c>
       <c r="I5" t="n">
-        <v>34026000</v>
+        <v>10089000</v>
       </c>
       <c r="J5" t="n">
-        <v>411000</v>
+        <v>316000</v>
       </c>
       <c r="K5" t="n">
-        <v>34332000</v>
+        <v>15121000</v>
       </c>
       <c r="L5" t="n">
-        <v>34332000</v>
+        <v>16403000</v>
       </c>
       <c r="M5" t="n">
-        <v>34332000</v>
+        <v>15121000</v>
       </c>
       <c r="N5" t="n">
-        <v>34332000</v>
+        <v>15121000</v>
       </c>
       <c r="O5" t="n">
-        <v>16436000</v>
+        <v>-2852000</v>
       </c>
       <c r="P5" t="n">
-        <v>12793000</v>
+        <v>14700000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1032000</v>
+        <v>1417000</v>
       </c>
       <c r="R5" t="n">
-        <v>1032000</v>
+        <v>1417000</v>
       </c>
       <c r="S5" t="n">
-        <v>42868000</v>
+        <v>34136000</v>
       </c>
       <c r="T5" t="n">
-        <v>160000</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>1972000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>588000</v>
+      </c>
       <c r="V5" t="n">
-        <v>160000</v>
+        <v>1384000</v>
       </c>
       <c r="W5" t="n">
-        <v>160000</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
+        <v>102000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1282000</v>
+      </c>
       <c r="Y5" t="n">
-        <v>42708000</v>
+        <v>32164000</v>
       </c>
       <c r="Z5" t="n">
-        <v>17398000</v>
+        <v>14107000</v>
       </c>
       <c r="AA5" t="n">
-        <v>251000</v>
+        <v>214000</v>
       </c>
       <c r="AB5" t="n">
-        <v>17147000</v>
+        <v>13893000</v>
       </c>
       <c r="AC5" t="n">
-        <v>24211000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>555000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>368000</v>
-      </c>
+        <v>13029000</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>23288000</v>
+        <v>13029000</v>
       </c>
       <c r="AG5" t="n">
-        <v>77200000</v>
+        <v>49257000</v>
       </c>
       <c r="AH5" t="n">
-        <v>9059000</v>
+        <v>12419000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1465000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>89000</v>
-      </c>
+        <v>2493000</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>6281000</v>
+        <v>4255000</v>
       </c>
       <c r="AL5" t="n">
-        <v>6281000</v>
+        <v>4255000</v>
       </c>
       <c r="AM5" t="n">
-        <v>306000</v>
+        <v>5032000</v>
       </c>
       <c r="AN5" t="n">
-        <v>20000</v>
+        <v>5032000</v>
       </c>
       <c r="AO5" t="n">
-        <v>286000</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>918000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-1173000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2091000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1002000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>969000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>120000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
+        <v>639000</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>68141000</v>
+        <v>36838000</v>
       </c>
       <c r="AX5" t="n">
-        <v>1245000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>2047000</v>
-      </c>
+        <v>1031000</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>14359000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>14359000</v>
-      </c>
+        <v>12030000</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>5102000</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>736000</v>
-      </c>
+        <v>11258000</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>36982000</v>
+        <v>9962000</v>
       </c>
       <c r="BE5" t="n">
-        <v>-483000</v>
+        <v>-1277000</v>
       </c>
       <c r="BF5" t="n">
-        <v>37465000</v>
+        <v>11239000</v>
       </c>
       <c r="BG5" t="n">
-        <v>7670000</v>
+        <v>2557000</v>
       </c>
       <c r="BH5" t="n">
-        <v>7670000</v>
-      </c>
-      <c r="BI5" t="inlineStr"/>
+        <v>2557000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>138000</v>
+      </c>
       <c r="BJ5" t="n">
-        <v>7670000</v>
+        <v>2419000</v>
       </c>
     </row>
   </sheetData>
@@ -2502,544 +2502,544 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>81000</v>
+        <v>-171000</v>
       </c>
       <c r="C2" t="n">
-        <v>-3105000</v>
+        <v>-65142000</v>
       </c>
       <c r="D2" t="n">
-        <v>5670000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>68928000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
       <c r="F2" t="n">
-        <v>-2086000</v>
+        <v>-57000</v>
       </c>
       <c r="G2" t="n">
-        <v>2557000</v>
+        <v>7670000</v>
       </c>
       <c r="H2" t="n">
-        <v>2536000</v>
+        <v>6042000</v>
       </c>
       <c r="I2" t="n">
-        <v>488000</v>
+        <v>180000</v>
       </c>
       <c r="J2" t="n">
-        <v>-467000</v>
+        <v>1448000</v>
       </c>
       <c r="K2" t="n">
-        <v>-184000</v>
+        <v>1970000</v>
       </c>
       <c r="L2" t="n">
-        <v>-2463000</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+        <v>-1362000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
       <c r="O2" t="n">
-        <v>2565000</v>
+        <v>3786000</v>
       </c>
       <c r="P2" t="n">
-        <v>1283000</v>
+        <v>9946000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3105000</v>
+        <v>-58982000</v>
       </c>
       <c r="R2" t="n">
-        <v>4388000</v>
+        <v>68928000</v>
       </c>
       <c r="S2" t="n">
-        <v>1282000</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
+        <v>-6160000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-6160000</v>
+      </c>
       <c r="U2" t="n">
-        <v>1282000</v>
+        <v>68928000</v>
       </c>
       <c r="V2" t="n">
-        <v>-2450000</v>
+        <v>-408000</v>
       </c>
       <c r="W2" t="n">
-        <v>-385000</v>
+        <v>-353000</v>
       </c>
       <c r="X2" t="n">
-        <v>21000</v>
+        <v>2000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-689000</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-689000</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-493000</v>
+        <v>-57000</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>-493000</v>
+        <v>-57000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-904000</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2167000</v>
+        <v>-114000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>-192000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-650000</v>
+        <v>-491000</v>
       </c>
       <c r="AH2" t="n">
-        <v>6464000</v>
+        <v>-4555000</v>
       </c>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>2174000</v>
+        <v>556000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-2419000</v>
+        <v>2195000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-2731000</v>
+        <v>-2443000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1940000</v>
+        <v>-2594000</v>
       </c>
       <c r="AN2" t="n">
-        <v>7500000</v>
+        <v>-2269000</v>
       </c>
       <c r="AO2" t="n">
-        <v>3066000</v>
+        <v>1794000</v>
       </c>
       <c r="AP2" t="n">
-        <v>100000</v>
+        <v>89000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>951000</v>
+        <v>647000</v>
       </c>
       <c r="AR2" t="n">
-        <v>70000</v>
+        <v>13000</v>
       </c>
       <c r="AS2" t="n">
-        <v>881000</v>
+        <v>634000</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>-7764000</v>
+        <v>2486000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>29876000</v>
+        <v>-1653000</v>
       </c>
       <c r="C3" t="n">
-        <v>-71504000</v>
+        <v>-39394000</v>
       </c>
       <c r="D3" t="n">
-        <v>44319000</v>
+        <v>35628000</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2292000</v>
       </c>
       <c r="F3" t="n">
-        <v>-790000</v>
+        <v>-1915000</v>
       </c>
       <c r="G3" t="n">
-        <v>2536000</v>
+        <v>2343000</v>
       </c>
       <c r="H3" t="n">
-        <v>2343000</v>
+        <v>7670000</v>
       </c>
       <c r="I3" t="n">
-        <v>-311000</v>
+        <v>-120000</v>
       </c>
       <c r="J3" t="n">
-        <v>504000</v>
+        <v>-5207000</v>
       </c>
       <c r="K3" t="n">
-        <v>-29911000</v>
+        <v>-2660000</v>
       </c>
       <c r="L3" t="n">
-        <v>-2284000</v>
+        <v>-816000</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2292000</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2292000</v>
       </c>
       <c r="O3" t="n">
-        <v>-27185000</v>
+        <v>-3766000</v>
       </c>
       <c r="P3" t="n">
-        <v>-27185000</v>
+        <v>-3766000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-71504000</v>
+        <v>-39394000</v>
       </c>
       <c r="R3" t="n">
-        <v>44319000</v>
+        <v>35628000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-251000</v>
+        <v>-2809000</v>
       </c>
       <c r="W3" t="n">
-        <v>523000</v>
+        <v>-905000</v>
       </c>
       <c r="X3" t="n">
-        <v>16000</v>
+        <v>11000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-409000</v>
+        <v>-431000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-409000</v>
+        <v>-431000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-381000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
+        <v>-8000</v>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>-381000</v>
+        <v>-8000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1518000</v>
+        <v>-1476000</v>
       </c>
       <c r="AE3" t="n">
-        <v>30666000</v>
+        <v>262000</v>
       </c>
       <c r="AF3" t="n">
-        <v>219000</v>
+        <v>31000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-800000</v>
+        <v>-739000</v>
       </c>
       <c r="AH3" t="n">
-        <v>34537000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-1518000</v>
-      </c>
+        <v>365000</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>1140000</v>
+        <v>41000</v>
       </c>
       <c r="AK3" t="n">
-        <v>35906000</v>
+        <v>-5067000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1530000</v>
+        <v>803000</v>
       </c>
       <c r="AM3" t="n">
-        <v>5272000</v>
+        <v>-6110000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-4733000</v>
+        <v>10698000</v>
       </c>
       <c r="AO3" t="n">
-        <v>2198000</v>
+        <v>1544000</v>
       </c>
       <c r="AP3" t="n">
-        <v>242000</v>
+        <v>465000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>802000</v>
+        <v>646000</v>
       </c>
       <c r="AR3" t="n">
-        <v>146000</v>
+        <v>64000</v>
       </c>
       <c r="AS3" t="n">
-        <v>656000</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
+        <v>582000</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>-8649000</v>
+        <v>-2077000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-1653000</v>
+        <v>29876000</v>
       </c>
       <c r="C4" t="n">
-        <v>-39394000</v>
+        <v>-71504000</v>
       </c>
       <c r="D4" t="n">
-        <v>35628000</v>
+        <v>44319000</v>
       </c>
       <c r="E4" t="n">
-        <v>2292000</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-1915000</v>
+        <v>-790000</v>
       </c>
       <c r="G4" t="n">
+        <v>2536000</v>
+      </c>
+      <c r="H4" t="n">
         <v>2343000</v>
       </c>
-      <c r="H4" t="n">
-        <v>7670000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-120000</v>
+        <v>-311000</v>
       </c>
       <c r="J4" t="n">
-        <v>-5207000</v>
+        <v>504000</v>
       </c>
       <c r="K4" t="n">
-        <v>-2660000</v>
+        <v>-29911000</v>
       </c>
       <c r="L4" t="n">
-        <v>-816000</v>
+        <v>-2284000</v>
       </c>
       <c r="M4" t="n">
-        <v>2292000</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2292000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-3766000</v>
+        <v>-27185000</v>
       </c>
       <c r="P4" t="n">
-        <v>-3766000</v>
+        <v>-27185000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-39394000</v>
+        <v>-71504000</v>
       </c>
       <c r="R4" t="n">
-        <v>35628000</v>
+        <v>44319000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
       <c r="V4" t="n">
-        <v>-2809000</v>
+        <v>-251000</v>
       </c>
       <c r="W4" t="n">
-        <v>-905000</v>
+        <v>523000</v>
       </c>
       <c r="X4" t="n">
-        <v>11000</v>
+        <v>16000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-431000</v>
+        <v>-409000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-431000</v>
+        <v>-409000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-8000</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+        <v>-381000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
       <c r="AC4" t="n">
-        <v>-8000</v>
+        <v>-381000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1476000</v>
+        <v>-1518000</v>
       </c>
       <c r="AE4" t="n">
-        <v>262000</v>
+        <v>30666000</v>
       </c>
       <c r="AF4" t="n">
-        <v>31000</v>
+        <v>219000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-739000</v>
+        <v>-800000</v>
       </c>
       <c r="AH4" t="n">
-        <v>365000</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
+        <v>34537000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-1518000</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>41000</v>
+        <v>1140000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-5067000</v>
+        <v>35906000</v>
       </c>
       <c r="AL4" t="n">
-        <v>803000</v>
+        <v>-1530000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-6110000</v>
+        <v>5272000</v>
       </c>
       <c r="AN4" t="n">
-        <v>10698000</v>
+        <v>-4733000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1544000</v>
+        <v>2198000</v>
       </c>
       <c r="AP4" t="n">
-        <v>465000</v>
+        <v>242000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>646000</v>
+        <v>802000</v>
       </c>
       <c r="AR4" t="n">
-        <v>64000</v>
+        <v>146000</v>
       </c>
       <c r="AS4" t="n">
-        <v>582000</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
+        <v>656000</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
       <c r="AU4" t="n">
-        <v>-2077000</v>
+        <v>-8649000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-171000</v>
+        <v>81000</v>
       </c>
       <c r="C5" t="n">
-        <v>-65142000</v>
+        <v>-3105000</v>
       </c>
       <c r="D5" t="n">
-        <v>68928000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
+        <v>5670000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>-57000</v>
+        <v>-2086000</v>
       </c>
       <c r="G5" t="n">
-        <v>7670000</v>
+        <v>2557000</v>
       </c>
       <c r="H5" t="n">
-        <v>6042000</v>
+        <v>2536000</v>
       </c>
       <c r="I5" t="n">
-        <v>180000</v>
+        <v>488000</v>
       </c>
       <c r="J5" t="n">
-        <v>1448000</v>
+        <v>-467000</v>
       </c>
       <c r="K5" t="n">
-        <v>1970000</v>
+        <v>-184000</v>
       </c>
       <c r="L5" t="n">
-        <v>-1362000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
+        <v>-2463000</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>3786000</v>
+        <v>2565000</v>
       </c>
       <c r="P5" t="n">
-        <v>9946000</v>
+        <v>1283000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-58982000</v>
+        <v>-3105000</v>
       </c>
       <c r="R5" t="n">
-        <v>68928000</v>
+        <v>4388000</v>
       </c>
       <c r="S5" t="n">
-        <v>-6160000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-6160000</v>
-      </c>
+        <v>1282000</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>68928000</v>
+        <v>1282000</v>
       </c>
       <c r="V5" t="n">
-        <v>-408000</v>
+        <v>-2450000</v>
       </c>
       <c r="W5" t="n">
-        <v>-353000</v>
+        <v>-385000</v>
       </c>
       <c r="X5" t="n">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-689000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-689000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-57000</v>
+        <v>-493000</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>-57000</v>
+        <v>-493000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>-904000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-114000</v>
+        <v>2167000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-192000</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>-491000</v>
+        <v>-650000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-4555000</v>
+        <v>6464000</v>
       </c>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>556000</v>
+        <v>2174000</v>
       </c>
       <c r="AK5" t="n">
-        <v>2195000</v>
+        <v>-2419000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-2443000</v>
+        <v>-2731000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-2594000</v>
+        <v>1940000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-2269000</v>
+        <v>7500000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1794000</v>
+        <v>3066000</v>
       </c>
       <c r="AP5" t="n">
-        <v>89000</v>
+        <v>100000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>647000</v>
+        <v>951000</v>
       </c>
       <c r="AR5" t="n">
-        <v>13000</v>
+        <v>70000</v>
       </c>
       <c r="AS5" t="n">
-        <v>634000</v>
+        <v>881000</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>2486000</v>
+        <v>-7764000</v>
       </c>
     </row>
   </sheetData>
@@ -3539,187 +3539,187 @@
       </c>
       <c r="CS1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
       <c r="CW1" t="inlineStr">
         <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>longName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
         </is>
       </c>
       <c r="ED1" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Keung  Lam', 'age': 52, 'title': 'Executive Chairman &amp; CEO', 'yearBorn': 1973, 'fiscalYear': 2025, 'totalPay': 1898223, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yu Pik  Cheng', 'age': 44, 'title': 'Head of Operations &amp; Executive Director', 'yearBorn': 1981, 'fiscalYear': 2025, 'totalPay': 1065889, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ka Man  Au', 'age': 42, 'title': 'CFO &amp; Company Secretary', 'yearBorn': 1983, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Keung  Lam', 'age': 52, 'title': 'Executive Chairman &amp; CEO', 'yearBorn': 1973, 'fiscalYear': 2025, 'totalPay': 1898149, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yu Pik  Cheng', 'age': 44, 'title': 'Head of Operations &amp; Executive Director', 'yearBorn': 1981, 'fiscalYear': 2025, 'totalPay': 1065847, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ka Man  Au', 'age': 42, 'title': 'CFO &amp; Company Secretary', 'yearBorn': 1983, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -3822,67 +3822,67 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.47</v>
+        <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="W2" t="n">
-        <v>0.495</v>
+        <v>1.63</v>
       </c>
       <c r="X2" t="n">
-        <v>0.72</v>
+        <v>1.83</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.47</v>
+        <v>1.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.495</v>
+        <v>1.63</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.277</v>
+        <v>-0.221</v>
       </c>
       <c r="AE2" t="n">
-        <v>17500100</v>
+        <v>817200</v>
       </c>
       <c r="AF2" t="n">
-        <v>17500100</v>
+        <v>817200</v>
       </c>
       <c r="AG2" t="n">
-        <v>529525</v>
+        <v>2131494</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>9557467</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>9557467</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.55</v>
+        <v>1.63</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.59</v>
+        <v>1.7</v>
       </c>
       <c r="AL2" t="n">
-        <v>73793576</v>
+        <v>224016208</v>
       </c>
       <c r="AM2" t="n">
-        <v>73793573</v>
+        <v>224016204</v>
       </c>
       <c r="AN2" t="n">
         <v>0.35</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.11</v>
+        <v>2.4</v>
       </c>
       <c r="AP2" t="n">
         <v>34.872528</v>
@@ -3891,13 +3891,13 @@
         <v>0.33</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.3610431</v>
+        <v>4.1317377</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.4576</v>
+        <v>0.7163</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.6371</v>
+        <v>0.67515</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>73055856</v>
+        <v>198241808</v>
       </c>
       <c r="AZ2" t="n">
         <v>-0.16590999</v>
@@ -3935,10 +3935,10 @@
         <v>131774238</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.3761549</v>
+        <v>0.3761844</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.4887484</v>
+        <v>4.5190606</v>
       </c>
       <c r="BH2" t="n">
         <v>1743379200</v>
@@ -3964,16 +3964,16 @@
         <v>1763683200</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.347</v>
+        <v>3.656</v>
       </c>
       <c r="BP2" t="n">
-        <v>-11.187</v>
+        <v>-30.356</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0.30864197</v>
+        <v>1.1428571</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="BT2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
@@ -4071,140 +4071,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CS2" t="n">
-        <v>19.148935</v>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>CONTEL</t>
+        </is>
       </c>
       <c r="CT2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
+        <v>-5.5555506</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>1.7</v>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>CONTEL</t>
+          <t>PRE</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>finmb_625908758</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DA2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>2131494</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>3.857143</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>0.35 - 2.4</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>-0.70000005</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.2916667</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>114.285706</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>1724852927</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>1724852927</v>
+      </c>
+      <c r="DN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0.98370004</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1.3733073</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>1.0248501</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1.5179592</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="CX2" t="n">
-        <v>1777882101</v>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>finmb_625908758</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DC2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>0.495 - 0.72</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DW2" t="n">
+        <v>1782115098</v>
+      </c>
+      <c r="DX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1563240600000</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.099999905</v>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>1.63 - 1.83</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DG2" t="n">
-        <v>529525</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>0.21000001</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>0.35 - 1.11</t>
-        </is>
-      </c>
-      <c r="DK2" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>-0.4954955</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>-30.864197</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>1724852927</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>1724852927</v>
-      </c>
-      <c r="DP2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.102400005</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.22377624</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.07709998</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.121017076</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1563240600000</v>
-      </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EC2" t="inlineStr">
         <is>
           <t>Contel Technology Company Limited</t>
         </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EC2" t="b">
-        <v>0</v>
       </c>
       <c r="ED2" t="inlineStr"/>
     </row>
